--- a/Codes_2025/Trial 3/Trial3_Proposed (ElasticNet)_Followers_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_Proposed (ElasticNet)_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,14 +478,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>37.81</v>
+        <v>33.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>37.22033627553438</v>
+        <v>138.2814749124051</v>
       </c>
       <c r="F2" t="n">
-        <v>62.23974990844727</v>
+        <v>127.6429595947266</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,23 +504,23 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>16.67290473774495</v>
+        <v>71.88865045828496</v>
       </c>
       <c r="I2" t="n">
-        <v>21.13709526225506</v>
+        <v>38.00865045828495</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>33.88</v>
+        <v>28.09</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>138.2814749124051</v>
+        <v>30.68767035587374</v>
       </c>
       <c r="F3" t="n">
-        <v>124.6201324462891</v>
+        <v>47.33953094482422</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>26.00460368074334</v>
+        <v>28.89074918970298</v>
       </c>
       <c r="I3" t="n">
-        <v>7.875396319256659</v>
+        <v>0.8007491897029801</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>28.09</v>
+        <v>19.89</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30.68767035587374</v>
+        <v>16.07039809120311</v>
       </c>
       <c r="F4" t="n">
-        <v>47.70660400390625</v>
+        <v>20.32815361022949</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,23 +574,23 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14.49884076509174</v>
+        <v>14.42769879088629</v>
       </c>
       <c r="I4" t="n">
-        <v>13.59115923490825</v>
+        <v>5.462301209113706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>24.26000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36.70529760187497</v>
+        <v>9.038987214440688</v>
       </c>
       <c r="F5" t="n">
-        <v>26.88743782043457</v>
+        <v>8.912322998046875</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11.38442909968466</v>
+        <v>8.315173263471204</v>
       </c>
       <c r="I5" t="n">
-        <v>12.87557090031534</v>
+        <v>3.284826736528798</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>19.89</v>
+        <v>10.68</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.07039809120311</v>
+        <v>12.34611016321944</v>
       </c>
       <c r="F6" t="n">
-        <v>18.15356063842773</v>
+        <v>9.84849739074707</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -644,23 +644,23 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.07789795717092</v>
+        <v>8.816441201643439</v>
       </c>
       <c r="I6" t="n">
-        <v>9.812102042829082</v>
+        <v>1.863558798356559</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>11.6</v>
+        <v>8.050000000000002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9.038987214440688</v>
+        <v>47.01637236983374</v>
       </c>
       <c r="F7" t="n">
-        <v>8.460026741027832</v>
+        <v>12.45907783508301</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -679,23 +679,23 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8.627808420297496</v>
+        <v>10.2142579833978</v>
       </c>
       <c r="I7" t="n">
-        <v>2.972191579702505</v>
+        <v>2.164257983397798</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>10.68</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12.34611016321944</v>
+        <v>13.45661751886732</v>
       </c>
       <c r="F8" t="n">
-        <v>13.08967876434326</v>
+        <v>11.49200439453125</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9.320374209970476</v>
+        <v>9.696445369224161</v>
       </c>
       <c r="I8" t="n">
-        <v>1.359625790029522</v>
+        <v>1.706445369224162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>8.050000000000002</v>
+        <v>7.740000000000002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.01637236983374</v>
+        <v>9.929802182220868</v>
       </c>
       <c r="F9" t="n">
-        <v>11.20903968811035</v>
+        <v>7.488900661468506</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -749,23 +749,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9.039042852805457</v>
+        <v>7.553011869858462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9890428528054542</v>
+        <v>0.1869881301415397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>7.989999999999999</v>
+        <v>5.93</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13.45661751886732</v>
+        <v>7.94460938405617</v>
       </c>
       <c r="F10" t="n">
-        <v>11.23635196685791</v>
+        <v>6.63538932800293</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -784,23 +784,23 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9.043128591820681</v>
+        <v>7.096005280414248</v>
       </c>
       <c r="I10" t="n">
-        <v>1.053128591820681</v>
+        <v>1.166005280414248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.740000000000002</v>
+        <v>5.56</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.929802182220868</v>
+        <v>3.665586355441213</v>
       </c>
       <c r="F11" t="n">
-        <v>7.97056245803833</v>
+        <v>3.968035221099854</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,23 +819,23 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8.554587751452802</v>
+        <v>5.667789443740821</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8145877514527999</v>
+        <v>0.1077894437408213</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.81</v>
+        <v>2.64</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.71820080519103</v>
+        <v>3.577960374161461</v>
       </c>
       <c r="F12" t="n">
-        <v>10.10855293273926</v>
+        <v>3.317789793014526</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -854,115 +854,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8.8744172016939</v>
+        <v>5.319620141542618</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0644172016939</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>7.94460938405617</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6.013400554656982</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>8.261809077741059</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.33180907774106</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>3.665586355441213</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3.754091262817383</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>7.923831122607869</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.363831122607869</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3.577960374161461</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3.204214334487915</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>7.841573115489068</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5.201573115489067</v>
+        <v>2.679620141542618</v>
       </c>
     </row>
   </sheetData>
